--- a/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_eventstudy_cosine_weighted_top_vs_bottom.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/unemployment/sdid_eventstudy_cosine_weighted_top_vs_bottom.xlsx
@@ -507,13 +507,13 @@
         <v>7.143494137888768</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.03980671070230369</v>
+        <v>-0.05054832921311191</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03981455431813342</v>
+        <v>0.05055617282894164</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>7.147143347946397</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.03980760561312114</v>
+        <v>-0.05054922412392936</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03981365940731597</v>
+        <v>0.05055527791812419</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>7.133707662794738</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.03979921854936919</v>
+        <v>-0.05054083706017742</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03982204647106791</v>
+        <v>0.05056366498187614</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>7.114353979997055</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.03980941183660037</v>
+        <v>-0.05055103034740859</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03981185318383674</v>
+        <v>0.05055347169464496</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>7.078860145819582</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.03980830413281745</v>
+        <v>-0.05054992264362567</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03981296088761966</v>
+        <v>0.05055457939842788</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>7.047498083327357</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.03980224137716349</v>
+        <v>-0.05054385988797171</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03981902364327362</v>
+        <v>0.05056064215408184</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>7.016173090253348</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.03980984504888774</v>
+        <v>-0.05055146355969597</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03981141997154936</v>
+        <v>0.05055303848235759</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>7.00740932089789</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.03980473403904129</v>
+        <v>-0.05054635254984951</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03981653098139582</v>
+        <v>0.05055814949220405</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>6.974505142875418</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.03980590283304953</v>
+        <v>-0.05054752134385775</v>
       </c>
       <c r="K10" t="n">
-        <v>0.03981536218738758</v>
+        <v>0.0505569806981958</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>6.955527058537186</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.03980229056617369</v>
+        <v>-0.05054390907698191</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03981897445426342</v>
+        <v>0.05056059296507164</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>6.928417635834625</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.03980590854464517</v>
+        <v>-0.05054752705545339</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03981535647579194</v>
+        <v>0.05055697498660016</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>6.899612613809318</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.03981354829983808</v>
+        <v>-0.05055516681064631</v>
       </c>
       <c r="K13" t="n">
-        <v>0.03980771672059902</v>
+        <v>0.05054933523140725</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>6.907681402022805</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.03979832580044019</v>
+        <v>-0.05053994431124841</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03982293921999692</v>
+        <v>0.05056455773080514</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>6.88986849628777</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.03980787168312806</v>
+        <v>-0.05054949019393628</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03981339333730905</v>
+        <v>0.05055501184811727</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>6.878651728246825</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.03980632978057753</v>
+        <v>-0.05054794829138575</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03981493523985958</v>
+        <v>0.0505565537506678</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>6.849672412668123</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.03980622378320931</v>
+        <v>-0.05054784229401754</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0398150412372278</v>
+        <v>0.05055665974803602</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>6.820501297855685</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.03980556781054734</v>
+        <v>-0.05054718632135557</v>
       </c>
       <c r="K18" t="n">
-        <v>0.03981569720988976</v>
+        <v>0.05055731572069799</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>6.807360183018594</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.03981016662711934</v>
+        <v>-0.05055178513792757</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03981109839331776</v>
+        <v>0.05055271690412599</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>6.835856398364068</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.03979764412690124</v>
+        <v>-0.05053926263770946</v>
       </c>
       <c r="K20" t="n">
-        <v>0.03982362089353587</v>
+        <v>0.05056523940434409</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>6.858921874755683</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.03981063251021855</v>
+        <v>-0.05055225102102678</v>
       </c>
       <c r="K21" t="n">
-        <v>0.03981063251021855</v>
+        <v>0.05055225102102678</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>6.837047353119154</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.02952871207413389</v>
+        <v>-0.04027033058494211</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05009255294630322</v>
+        <v>0.06083417145711145</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>6.827210393763395</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.01958670673937935</v>
+        <v>-0.03032832525018758</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06003455828105776</v>
+        <v>0.07077617679186599</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>6.819310755174234</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.01890690571147858</v>
+        <v>-0.0296485242222868</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06071435930895853</v>
+        <v>0.07145597781976676</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>6.804921446601844</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.01150634432552967</v>
+        <v>-0.02224796283633789</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06811492069490743</v>
+        <v>0.07885653920571567</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>6.832986813162061</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.01754908277500356</v>
+        <v>-0.02829070128581179</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06207218224543355</v>
+        <v>0.07281380075624178</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>6.824299820508662</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.007372080911597585</v>
+        <v>-0.01811369942240581</v>
       </c>
       <c r="K27" t="n">
-        <v>0.07224918410883951</v>
+        <v>0.08299080261964775</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>6.793843711629481</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J28" t="n">
-        <v>0.01531333733021788</v>
+        <v>0.004571718819409661</v>
       </c>
       <c r="K28" t="n">
-        <v>0.09493460235065498</v>
+        <v>0.1056762208614632</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>6.77235016771745</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J29" t="n">
-        <v>0.01186551748094632</v>
+        <v>0.0011238989701381</v>
       </c>
       <c r="K29" t="n">
-        <v>0.09148678250138342</v>
+        <v>0.1022284010121917</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>6.760430696919773</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J30" t="n">
-        <v>0.01176459147434982</v>
+        <v>0.001022972963541598</v>
       </c>
       <c r="K30" t="n">
-        <v>0.09138585649478692</v>
+        <v>0.1021274750055952</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>6.755819906146019</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J31" t="n">
-        <v>0.01721815132680948</v>
+        <v>0.006476532816001253</v>
       </c>
       <c r="K31" t="n">
-        <v>0.09683941634724658</v>
+        <v>0.1075810348580548</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>6.779495036993018</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J32" t="n">
-        <v>0.015349104214323</v>
+        <v>0.004607485703514776</v>
       </c>
       <c r="K32" t="n">
-        <v>0.0949703692347601</v>
+        <v>0.1057119877455683</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>6.791536491586684</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02491225087212978</v>
+        <v>0.01417063236132155</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1045335158925669</v>
+        <v>0.1152751344033751</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>6.780104979292171</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J34" t="n">
-        <v>0.03787562170969671</v>
+        <v>0.02713400319888849</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1174968867301338</v>
+        <v>0.128238505240942</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>6.786512127625599</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J35" t="n">
-        <v>0.03795773440795357</v>
+        <v>0.02721611589714535</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1175789994283907</v>
+        <v>0.1283206179391989</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>6.773552910378499</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J36" t="n">
-        <v>0.04124755655206157</v>
+        <v>0.03050593804125335</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1208688215724987</v>
+        <v>0.1316104400833069</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>6.762874755721914</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J37" t="n">
-        <v>0.04480219307472488</v>
+        <v>0.03406057456391665</v>
       </c>
       <c r="K37" t="n">
-        <v>0.124423458095162</v>
+        <v>0.1351650766059702</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>6.779893131165665</v>
       </c>
       <c r="I38" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J38" t="n">
-        <v>0.03758370128850429</v>
+        <v>0.02684208277769607</v>
       </c>
       <c r="K38" t="n">
-        <v>0.1172049663089414</v>
+        <v>0.1279465848197496</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>6.777213173440835</v>
       </c>
       <c r="I39" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03590566036975317</v>
+        <v>0.02516404185894495</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1155269253901903</v>
+        <v>0.1262685439009985</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>6.774573791669479</v>
       </c>
       <c r="I40" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J40" t="n">
-        <v>0.03703695863610878</v>
+        <v>0.02629534012530056</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1166582236565459</v>
+        <v>0.1273998421673541</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>6.741461528590615</v>
       </c>
       <c r="I41" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0474661502035536</v>
+        <v>0.03672453169274537</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1270874152239907</v>
+        <v>0.1378290337347989</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>6.724206067579491</v>
       </c>
       <c r="I42" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J42" t="n">
-        <v>0.04400202553402365</v>
+        <v>0.03326040702321543</v>
       </c>
       <c r="K42" t="n">
-        <v>0.1236232905544608</v>
+        <v>0.134364909065269</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>6.706270733121253</v>
       </c>
       <c r="I43" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J43" t="n">
-        <v>0.04686719947759776</v>
+        <v>0.03612558096678953</v>
       </c>
       <c r="K43" t="n">
-        <v>0.1264884644980349</v>
+        <v>0.1372300830088431</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>6.734098000710415</v>
       </c>
       <c r="I44" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J44" t="n">
-        <v>0.04276503407097731</v>
+        <v>0.03202341556016908</v>
       </c>
       <c r="K44" t="n">
-        <v>0.1223862990914144</v>
+        <v>0.1331279176022226</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>6.756865399212114</v>
       </c>
       <c r="I45" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J45" t="n">
-        <v>0.04718168864807026</v>
+        <v>0.03644007013726203</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1268029536685074</v>
+        <v>0.1375445721793156</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>6.738006495406657</v>
       </c>
       <c r="I46" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J46" t="n">
-        <v>0.05607665931653382</v>
+        <v>0.0453350408057256</v>
       </c>
       <c r="K46" t="n">
-        <v>0.1356979243369709</v>
+        <v>0.1464395428477792</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>6.74310740535934</v>
       </c>
       <c r="I47" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J47" t="n">
-        <v>0.05631642218582299</v>
+        <v>0.04557480367501477</v>
       </c>
       <c r="K47" t="n">
-        <v>0.1359376872062601</v>
+        <v>0.1466793057170683</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>6.732968250423442</v>
       </c>
       <c r="I48" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J48" t="n">
-        <v>0.06495043801998701</v>
+        <v>0.05420881950917878</v>
       </c>
       <c r="K48" t="n">
-        <v>0.1445717030404241</v>
+        <v>0.1553133215512323</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>6.729910181438982</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J49" t="n">
-        <v>0.06397953637811327</v>
+        <v>0.05323791786730504</v>
       </c>
       <c r="K49" t="n">
-        <v>0.1436008013985504</v>
+        <v>0.1543424199093586</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>6.741895706671492</v>
       </c>
       <c r="I50" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J50" t="n">
-        <v>0.06092689347023849</v>
+        <v>0.05018527495943027</v>
       </c>
       <c r="K50" t="n">
-        <v>0.1405481584906756</v>
+        <v>0.1512897770014838</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>6.734431556692429</v>
       </c>
       <c r="I51" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J51" t="n">
-        <v>0.07272004802555898</v>
+        <v>0.06197842951475075</v>
       </c>
       <c r="K51" t="n">
-        <v>0.1523413130459961</v>
+        <v>0.1630829315568043</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>6.726260387671091</v>
       </c>
       <c r="I52" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J52" t="n">
-        <v>0.07578091200433867</v>
+        <v>0.06503929349353044</v>
       </c>
       <c r="K52" t="n">
-        <v>0.1554021770247758</v>
+        <v>0.166143795535584</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>6.689848076031109</v>
       </c>
       <c r="I53" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J53" t="n">
-        <v>0.08337176078410202</v>
+        <v>0.07263014227329379</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1629930258045391</v>
+        <v>0.1737346443153474</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>6.676075412416227</v>
       </c>
       <c r="I54" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J54" t="n">
-        <v>0.0845720484290835</v>
+        <v>0.07383042991827526</v>
       </c>
       <c r="K54" t="n">
-        <v>0.1641933134495206</v>
+        <v>0.1749349319603288</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>6.663659716321614</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J55" t="n">
-        <v>0.08652090094140696</v>
+        <v>0.07577928243059873</v>
       </c>
       <c r="K55" t="n">
-        <v>0.1661421659618441</v>
+        <v>0.1768837844726523</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>6.689169577841492</v>
       </c>
       <c r="I56" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J56" t="n">
-        <v>0.09242528350648271</v>
+        <v>0.08168366499567448</v>
       </c>
       <c r="K56" t="n">
-        <v>0.1720465485269198</v>
+        <v>0.182788167037728</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>6.711158072789449</v>
       </c>
       <c r="I57" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J57" t="n">
-        <v>0.0931144728526645</v>
+        <v>0.08237285434185626</v>
       </c>
       <c r="K57" t="n">
-        <v>0.1727357378731016</v>
+        <v>0.1834773563839098</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>6.690328392176552</v>
       </c>
       <c r="I58" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J58" t="n">
-        <v>0.1096188451113385</v>
+        <v>0.09887722660053022</v>
       </c>
       <c r="K58" t="n">
-        <v>0.1892401101317756</v>
+        <v>0.1999817286425838</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>6.696640714886168</v>
       </c>
       <c r="I59" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J59" t="n">
-        <v>0.1057263724603414</v>
+        <v>0.09498475394953321</v>
       </c>
       <c r="K59" t="n">
-        <v>0.1853476374807785</v>
+        <v>0.1960892559915868</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>6.686251051535382</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J60" t="n">
-        <v>0.113652392329886</v>
+        <v>0.1029107738190778</v>
       </c>
       <c r="K60" t="n">
-        <v>0.1932736573503231</v>
+        <v>0.2040152758611313</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>6.688228171679967</v>
       </c>
       <c r="I61" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J61" t="n">
-        <v>0.1063943409654069</v>
+        <v>0.09565272245459866</v>
       </c>
       <c r="K61" t="n">
-        <v>0.186015605985844</v>
+        <v>0.1967572244966522</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>6.685622799336057</v>
       </c>
       <c r="I62" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1153854362088156</v>
+        <v>0.1046438176980073</v>
       </c>
       <c r="K62" t="n">
-        <v>0.1950067012292527</v>
+        <v>0.2057483197400609</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>6.689270749001296</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J63" t="n">
-        <v>0.1154210393234472</v>
+        <v>0.1046794208126389</v>
       </c>
       <c r="K63" t="n">
-        <v>0.1950423043438843</v>
+        <v>0.2057839228546925</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>6.679500555685947</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0203115471990911</v>
+        <v>0.02579196480664632</v>
       </c>
       <c r="J64" t="n">
-        <v>0.132003560761822</v>
+        <v>0.1212619422510137</v>
       </c>
       <c r="K64" t="n">
-        <v>0.2116248257822591</v>
+        <v>0.2223664442930673</v>
       </c>
     </row>
   </sheetData>
